--- a/data/trans_orig/BARTHEL_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/BARTHEL_R2-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2007</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>905</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27528</t>
+          <t>26958</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34490</t>
+          <t>34481</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31286</t>
+          <t>30119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62647</t>
+          <t>62713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72578</t>
+          <t>72052</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21908</t>
+          <t>21292</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9698</t>
+          <t>9978</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25393</t>
+          <t>25630</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58752</t>
+          <t>58561</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65706</t>
+          <t>65692</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75967</t>
+          <t>76583</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90058</t>
+          <t>90563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>139136</t>
+          <t>138899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154831</t>
+          <t>154551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18634</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23004</t>
+          <t>22558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43048</t>
+          <t>43135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50060</t>
+          <t>50050</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64887</t>
+          <t>65150</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78108</t>
+          <t>77208</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111457</t>
+          <t>111903</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126644</t>
+          <t>126470</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>818</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18818</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23012</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48952</t>
+          <t>48229</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54307</t>
+          <t>54304</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55495</t>
+          <t>55323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67911</t>
+          <t>67969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>106424</t>
+          <t>107642</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121056</t>
+          <t>121303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>14915</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27568</t>
+          <t>27487</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26243</t>
+          <t>26331</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37086</t>
+          <t>36925</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48970</t>
+          <t>49419</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62345</t>
+          <t>62411</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17207</t>
+          <t>17858</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21306</t>
+          <t>21614</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38901</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46265</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53102</t>
+          <t>52451</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65938</t>
+          <t>65487</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>96200</t>
+          <t>95892</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110875</t>
+          <t>110218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16722</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95858</t>
+          <t>96311</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104196</t>
+          <t>104242</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>106429</t>
+          <t>106000</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>115332</t>
+          <t>115308</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>206327</t>
+          <t>206851</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>218455</t>
+          <t>218345</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8212</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22614</t>
+          <t>22601</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19849</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41213</t>
+          <t>39823</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33257</t>
+          <t>32666</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59158</t>
+          <t>58652</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89279</t>
+          <t>89292</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>103681</t>
+          <t>103281</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>112012</t>
+          <t>113402</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>133376</t>
+          <t>133297</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>205960</t>
+          <t>206466</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>231861</t>
+          <t>232452</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,68%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29898</t>
+          <t>29182</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53228</t>
+          <t>52301</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>74229</t>
+          <t>73382</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>111261</t>
+          <t>109071</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>112046</t>
+          <t>109799</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>155501</t>
+          <t>153994</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>449238</t>
+          <t>450165</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>472568</t>
+          <t>473284</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>565581</t>
+          <t>567771</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>602613</t>
+          <t>603460</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1023807</t>
+          <t>1025314</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1067262</t>
+          <t>1069509</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2012</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15160</t>
+          <t>15052</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29238</t>
+          <t>29385</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>20073</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39609</t>
+          <t>38169</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31300</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41301</t>
+          <t>41325</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>19509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33734</t>
+          <t>33842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53566</t>
+          <t>55006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72637</t>
+          <t>73102</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22892</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25560</t>
+          <t>25484</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>45027</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35282</t>
+          <t>35683</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61395</t>
+          <t>61390</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56311</t>
+          <t>56496</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72814</t>
+          <t>72623</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57212</t>
+          <t>57066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76533</t>
+          <t>76609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>119901</t>
+          <t>119906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>146014</t>
+          <t>145613</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11401</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26838</t>
+          <t>26479</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18633</t>
+          <t>18860</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37344</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39576</t>
+          <t>38362</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51575</t>
+          <t>51526</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53130</t>
+          <t>53489</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68567</t>
+          <t>68696</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>98366</t>
+          <t>97018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117077</t>
+          <t>116850</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,1%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15512</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28572</t>
+          <t>29106</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20023</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39871</t>
+          <t>39538</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48516</t>
+          <t>48214</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59881</t>
+          <t>59661</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57002</t>
+          <t>56468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72618</t>
+          <t>72855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109731</t>
+          <t>110064</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129579</t>
+          <t>129243</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,39%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>12531</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21786</t>
+          <t>22160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30170</t>
+          <t>30295</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>19081</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28576</t>
+          <t>28751</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>27695</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40352</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51297</t>
+          <t>51172</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67633</t>
+          <t>67088</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,35%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19068</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12578</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27246</t>
+          <t>27413</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>21651</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41153</t>
+          <t>40396</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32688</t>
+          <t>32779</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45282</t>
+          <t>45333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42966</t>
+          <t>42799</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57634</t>
+          <t>58420</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80815</t>
+          <t>81572</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>99718</t>
+          <t>100317</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,25%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26726</t>
+          <t>26926</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21889</t>
+          <t>21805</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42331</t>
+          <t>41969</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35816</t>
+          <t>35766</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62232</t>
+          <t>61714</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85537</t>
+          <t>85337</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103034</t>
+          <t>103097</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>99631</t>
+          <t>99993</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>120073</t>
+          <t>120157</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>191994</t>
+          <t>192512</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>218410</t>
+          <t>218460</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>23156</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42752</t>
+          <t>43291</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31696</t>
+          <t>31204</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57301</t>
+          <t>57704</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>100510</t>
+          <t>101857</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>115473</t>
+          <t>116265</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>121665</t>
+          <t>121126</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>142393</t>
+          <t>141261</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>227868</t>
+          <t>227465</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>253473</t>
+          <t>253965</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>65298</t>
+          <t>65275</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>103386</t>
+          <t>101241</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>167530</t>
+          <t>171211</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>217976</t>
+          <t>219312</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>246375</t>
+          <t>246971</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>305797</t>
+          <t>309586</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>456251</t>
+          <t>458396</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>494339</t>
+          <t>494362</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>524999</t>
+          <t>523663</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>575445</t>
+          <t>571764</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>996815</t>
+          <t>993026</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1056237</t>
+          <t>1055641</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,04%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2016</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16019</t>
+          <t>16157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>11343</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25767</t>
+          <t>26257</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19444</t>
+          <t>20084</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37622</t>
+          <t>38806</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22877</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33257</t>
+          <t>33234</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23624</t>
+          <t>23134</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38090</t>
+          <t>38048</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50665</t>
+          <t>49481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68843</t>
+          <t>68203</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11179</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15682</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36426</t>
+          <t>37897</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20400</t>
+          <t>20728</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42980</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76116</t>
+          <t>76021</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85415</t>
+          <t>85371</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78802</t>
+          <t>77331</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99546</t>
+          <t>98242</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>159543</t>
+          <t>158644</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182123</t>
+          <t>181795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>11141</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>17015</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22955</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53138</t>
+          <t>52405</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61881</t>
+          <t>61539</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63428</t>
+          <t>62882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76607</t>
+          <t>76277</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>120488</t>
+          <t>120975</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136315</t>
+          <t>136301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18436</t>
+          <t>17846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12525</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32488</t>
+          <t>31028</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21200</t>
+          <t>21736</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42042</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46276</t>
+          <t>46866</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58574</t>
+          <t>58219</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59086</t>
+          <t>60546</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79049</t>
+          <t>78904</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114243</t>
+          <t>113374</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135085</t>
+          <t>134549</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18177</t>
+          <t>18377</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20987</t>
+          <t>21043</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36481</t>
+          <t>36960</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32355</t>
+          <t>32155</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44699</t>
+          <t>43971</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71625</t>
+          <t>71569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>85536</t>
+          <t>85321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16587</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>15001</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30966</t>
+          <t>32096</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>23597</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43419</t>
+          <t>43176</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31859</t>
+          <t>31914</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42632</t>
+          <t>42569</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36422</t>
+          <t>35292</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53500</t>
+          <t>52387</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72415</t>
+          <t>72658</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92239</t>
+          <t>92237</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22717</t>
+          <t>23034</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30103</t>
+          <t>29266</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53097</t>
+          <t>51759</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41911</t>
+          <t>42124</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69124</t>
+          <t>68887</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89468</t>
+          <t>89151</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103542</t>
+          <t>103738</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>94528</t>
+          <t>95866</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>117522</t>
+          <t>118359</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>190686</t>
+          <t>190923</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>217899</t>
+          <t>217686</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,79%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20781</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14368</t>
+          <t>15239</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34970</t>
+          <t>36198</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25621</t>
+          <t>25013</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49797</t>
+          <t>50383</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>113387</t>
+          <t>114047</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>127296</t>
+          <t>127774</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>141327</t>
+          <t>140099</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>161929</t>
+          <t>161058</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>260668</t>
+          <t>260082</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>284844</t>
+          <t>285452</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>56089</t>
+          <t>56165</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>85115</t>
+          <t>86052</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>144700</t>
+          <t>145837</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>195885</t>
+          <t>198271</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>212065</t>
+          <t>210422</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>273597</t>
+          <t>267800</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>506213</t>
+          <t>505276</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>535239</t>
+          <t>535163</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>582046</t>
+          <t>579660</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>633231</t>
+          <t>632094</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1095662</t>
+          <t>1101459</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1157194</t>
+          <t>1158837</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2023</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>13654</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>17731</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48151</t>
+          <t>47432</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55005</t>
+          <t>54524</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49741</t>
+          <t>49755</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58379</t>
+          <t>58750</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101379</t>
+          <t>101579</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112058</t>
+          <t>112167</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28105</t>
+          <t>28271</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42642</t>
+          <t>43581</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35627</t>
+          <t>35571</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55291</t>
+          <t>55028</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64827</t>
+          <t>64580</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75602</t>
+          <t>75529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85756</t>
+          <t>84817</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100293</t>
+          <t>100127</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>153816</t>
+          <t>154079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173480</t>
+          <t>173536</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24121</t>
+          <t>24620</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16587</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28828</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33361</t>
+          <t>32918</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49535</t>
+          <t>49509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49369</t>
+          <t>48870</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60803</t>
+          <t>60678</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56608</t>
+          <t>56940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68849</t>
+          <t>68303</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109391</t>
+          <t>109417</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125565</t>
+          <t>126008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>11695</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>16274</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26239</t>
+          <t>26980</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21980</t>
+          <t>22258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34890</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63254</t>
+          <t>62973</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71055</t>
+          <t>71131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77397</t>
+          <t>76656</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87396</t>
+          <t>87362</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143413</t>
+          <t>143592</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>156323</t>
+          <t>156045</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>17367</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25023</t>
+          <t>25048</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>24889</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30904</t>
+          <t>31052</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40810</t>
+          <t>41181</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48667</t>
+          <t>48694</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67818</t>
+          <t>67793</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77660</t>
+          <t>78000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>84,01%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>17832</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>16750</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26210</t>
+          <t>25667</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28675</t>
+          <t>29479</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41873</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41687</t>
+          <t>42429</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50501</t>
+          <t>50495</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39048</t>
+          <t>39591</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48123</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83646</t>
+          <t>83850</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96844</t>
+          <t>96040</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>76,51%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21463</t>
+          <t>21518</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89582</t>
+          <t>89449</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90099</t>
+          <t>89445</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>101060</t>
+          <t>101005</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>113810</t>
+          <t>113957</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>247924</t>
+          <t>248057</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>328649</t>
+          <t>330148</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>369930</t>
+          <t>370584</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>445256</t>
+          <t>444901</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8023</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18489</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26729</t>
+          <t>27255</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42591</t>
+          <t>43754</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>36629</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58255</t>
+          <t>55616</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>127986</t>
+          <t>127467</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>138452</t>
+          <t>138145</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>143028</t>
+          <t>141865</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>158890</t>
+          <t>158364</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>273839</t>
+          <t>276478</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>294576</t>
+          <t>295465</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>71941</t>
+          <t>71839</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>98875</t>
+          <t>99136</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>108560</t>
+          <t>100373</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>243644</t>
+          <t>241687</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>192746</t>
+          <t>172260</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>319041</t>
+          <t>320343</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>549445</t>
+          <t>549184</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>576379</t>
+          <t>576481</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>784166</t>
+          <t>786123</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>919250</t>
+          <t>927437</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1357089</t>
+          <t>1355787</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1483384</t>
+          <t>1503870</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/BARTHEL_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/BARTHEL_R2-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>7176</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26958</t>
+          <t>27253</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34481</t>
+          <t>34501</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30119</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62713</t>
+          <t>62761</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72052</t>
+          <t>72055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7312</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21292</t>
+          <t>22105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9978</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25630</t>
+          <t>25362</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58561</t>
+          <t>58616</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76583</t>
+          <t>75770</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90563</t>
+          <t>90328</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>138899</t>
+          <t>139167</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154551</t>
+          <t>154539</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18371</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22558</t>
+          <t>22323</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43135</t>
+          <t>42898</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50050</t>
+          <t>50047</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65150</t>
+          <t>64641</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77208</t>
+          <t>77951</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111903</t>
+          <t>112138</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126470</t>
+          <t>126336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>22324</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48229</t>
+          <t>48156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54304</t>
+          <t>54299</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55323</t>
+          <t>54998</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67969</t>
+          <t>68023</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>107642</t>
+          <t>107112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121303</t>
+          <t>121339</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14915</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>21389</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19787</t>
+          <t>19860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27487</t>
+          <t>26967</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26331</t>
+          <t>26240</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36925</t>
+          <t>37632</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49419</t>
+          <t>49204</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62411</t>
+          <t>62688</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17858</t>
+          <t>17397</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21614</t>
+          <t>21845</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37961</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46258</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52451</t>
+          <t>52912</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65487</t>
+          <t>65746</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95892</t>
+          <t>95661</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110218</t>
+          <t>110059</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>15798</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>96311</t>
+          <t>96237</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104242</t>
+          <t>104245</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>106000</t>
+          <t>106133</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>115308</t>
+          <t>115190</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>206851</t>
+          <t>207251</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>218345</t>
+          <t>218623</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>23160</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39823</t>
+          <t>41196</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32666</t>
+          <t>32616</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58652</t>
+          <t>58065</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89292</t>
+          <t>88733</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>103281</t>
+          <t>103275</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>113402</t>
+          <t>112029</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>133297</t>
+          <t>132922</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>206466</t>
+          <t>207053</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>232452</t>
+          <t>232502</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29182</t>
+          <t>31162</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>52301</t>
+          <t>53936</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>73382</t>
+          <t>75498</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>109071</t>
+          <t>111199</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>109799</t>
+          <t>110431</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>153994</t>
+          <t>153159</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>450165</t>
+          <t>448530</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>473284</t>
+          <t>471304</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>567771</t>
+          <t>565643</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>603460</t>
+          <t>601344</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1025314</t>
+          <t>1026149</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1069509</t>
+          <t>1068877</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>13261</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15052</t>
+          <t>15839</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>29537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20073</t>
+          <t>20314</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38169</t>
+          <t>39148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31195</t>
+          <t>31020</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41325</t>
+          <t>41323</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19509</t>
+          <t>19357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33842</t>
+          <t>33055</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55006</t>
+          <t>54027</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73102</t>
+          <t>72861</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,2%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22707</t>
+          <t>21760</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>25965</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45027</t>
+          <t>45107</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35683</t>
+          <t>36504</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61390</t>
+          <t>61358</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56496</t>
+          <t>57443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72623</t>
+          <t>73491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57066</t>
+          <t>56986</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76609</t>
+          <t>76128</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>119906</t>
+          <t>119938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145613</t>
+          <t>144792</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,86%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17380</t>
+          <t>17235</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26479</t>
+          <t>26625</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18860</t>
+          <t>19337</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38362</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51526</t>
+          <t>51495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53489</t>
+          <t>53343</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68696</t>
+          <t>68825</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>97018</t>
+          <t>97132</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116850</t>
+          <t>116373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15814</t>
+          <t>15409</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12719</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29106</t>
+          <t>29052</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20359</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39538</t>
+          <t>39617</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48214</t>
+          <t>48619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59661</t>
+          <t>59878</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56468</t>
+          <t>56522</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72855</t>
+          <t>71811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>110064</t>
+          <t>109985</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129243</t>
+          <t>129377</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22160</t>
+          <t>20839</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14379</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30295</t>
+          <t>30683</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28751</t>
+          <t>29227</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27695</t>
+          <t>29016</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40352</t>
+          <t>41665</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51172</t>
+          <t>50784</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67088</t>
+          <t>67510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,87%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18977</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27413</t>
+          <t>27391</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21651</t>
+          <t>21760</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40396</t>
+          <t>40421</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32779</t>
+          <t>33631</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45333</t>
+          <t>45356</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42799</t>
+          <t>42821</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58420</t>
+          <t>57616</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81572</t>
+          <t>81547</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100317</t>
+          <t>100208</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26926</t>
+          <t>27434</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21805</t>
+          <t>21734</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41969</t>
+          <t>42998</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35766</t>
+          <t>35574</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61714</t>
+          <t>62769</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85337</t>
+          <t>84829</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103097</t>
+          <t>102194</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>99993</t>
+          <t>98964</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>120157</t>
+          <t>120228</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>192512</t>
+          <t>191457</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>218460</t>
+          <t>218652</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18895</t>
+          <t>20440</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23156</t>
+          <t>23074</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43291</t>
+          <t>44509</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31204</t>
+          <t>32455</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57704</t>
+          <t>57648</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>101857</t>
+          <t>100312</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>116265</t>
+          <t>115248</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>121126</t>
+          <t>119908</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>141261</t>
+          <t>141343</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>227465</t>
+          <t>227521</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>253965</t>
+          <t>252714</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,62%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>65275</t>
+          <t>67035</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>101241</t>
+          <t>102984</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>171211</t>
+          <t>166780</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>219312</t>
+          <t>215353</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>246971</t>
+          <t>247130</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>309586</t>
+          <t>306910</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>458396</t>
+          <t>456653</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>494362</t>
+          <t>492602</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>523663</t>
+          <t>527622</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>571764</t>
+          <t>576195</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>993026</t>
+          <t>995702</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1055641</t>
+          <t>1055482</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,03%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16157</t>
+          <t>15399</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11343</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26257</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20084</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38806</t>
+          <t>37634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>42,63%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22739</t>
+          <t>23497</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>33257</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23134</t>
+          <t>24331</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38048</t>
+          <t>38350</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49481</t>
+          <t>50653</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68203</t>
+          <t>68518</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16986</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37897</t>
+          <t>36190</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20728</t>
+          <t>21127</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43879</t>
+          <t>43134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76021</t>
+          <t>75571</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85371</t>
+          <t>85033</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77331</t>
+          <t>79038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>98242</t>
+          <t>99120</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>158644</t>
+          <t>159389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181795</t>
+          <t>181396</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17015</t>
+          <t>16491</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22468</t>
+          <t>23638</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52405</t>
+          <t>53456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61539</t>
+          <t>61276</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62882</t>
+          <t>63406</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76277</t>
+          <t>77289</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>120975</t>
+          <t>119805</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136301</t>
+          <t>135864</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>18048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>12172</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31028</t>
+          <t>30417</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21736</t>
+          <t>21816</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42911</t>
+          <t>43032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46866</t>
+          <t>46664</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58219</t>
+          <t>58502</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60546</t>
+          <t>61157</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78904</t>
+          <t>79402</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>113374</t>
+          <t>113253</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>134549</t>
+          <t>134469</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>17854</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21043</t>
+          <t>20207</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36960</t>
+          <t>36336</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32155</t>
+          <t>32678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43971</t>
+          <t>44879</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71569</t>
+          <t>72405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>85321</t>
+          <t>85599</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,43%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>15602</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15001</t>
+          <t>13837</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32096</t>
+          <t>31067</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23597</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43176</t>
+          <t>43140</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31914</t>
+          <t>32844</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42569</t>
+          <t>43303</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35292</t>
+          <t>36321</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52387</t>
+          <t>53551</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72658</t>
+          <t>72694</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92237</t>
+          <t>92719</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>80,05%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23034</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29266</t>
+          <t>28306</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51759</t>
+          <t>52009</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42124</t>
+          <t>40933</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68887</t>
+          <t>67588</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89151</t>
+          <t>89525</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103738</t>
+          <t>103158</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>95866</t>
+          <t>95616</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>118359</t>
+          <t>119319</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>190923</t>
+          <t>192222</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>217686</t>
+          <t>218877</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>84,24%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>21105</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15239</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36198</t>
+          <t>35620</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25013</t>
+          <t>25636</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50383</t>
+          <t>50664</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>114047</t>
+          <t>113063</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>127774</t>
+          <t>127309</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140099</t>
+          <t>140677</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>161058</t>
+          <t>160930</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>260082</t>
+          <t>259801</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>285452</t>
+          <t>284829</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,74%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>56165</t>
+          <t>56185</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>86052</t>
+          <t>86038</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>145837</t>
+          <t>145972</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>198271</t>
+          <t>195591</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>210422</t>
+          <t>211551</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>267800</t>
+          <t>270154</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>505276</t>
+          <t>505290</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>535163</t>
+          <t>535143</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>579660</t>
+          <t>582340</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>632094</t>
+          <t>631959</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1101459</t>
+          <t>1099105</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1158837</t>
+          <t>1157708</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8469</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13654</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17731</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52630</t>
+          <t>57774</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47432</t>
+          <t>52877</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54524</t>
+          <t>60074</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55057</t>
+          <t>56768</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49755</t>
+          <t>52523</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58750</t>
+          <t>60239</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>107687</t>
+          <t>114541</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101579</t>
+          <t>108866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112167</t>
+          <t>119155</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>16816</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35305</t>
+          <t>37855</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28271</t>
+          <t>30464</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43581</t>
+          <t>46590</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>44902</t>
+          <t>48152</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35571</t>
+          <t>38462</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55028</t>
+          <t>58910</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>71112</t>
+          <t>78076</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64580</t>
+          <t>71557</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75529</t>
+          <t>82805</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>93093</t>
+          <t>96864</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84817</t>
+          <t>88129</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100127</t>
+          <t>104255</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>164205</t>
+          <t>174940</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154079</t>
+          <t>164182</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173536</t>
+          <t>184630</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,76%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>128398</t>
+          <t>134719</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128398</t>
+          <t>134719</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>128398</t>
+          <t>134719</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>209107</t>
+          <t>223092</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>209107</t>
+          <t>223092</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>209107</t>
+          <t>223092</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>17879</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24620</t>
+          <t>23170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22472</t>
+          <t>22713</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17133</t>
+          <t>17293</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28496</t>
+          <t>28906</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>40847</t>
+          <t>40593</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32918</t>
+          <t>33366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49509</t>
+          <t>48891</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55115</t>
+          <t>54406</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48870</t>
+          <t>49115</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60678</t>
+          <t>59411</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62964</t>
+          <t>61353</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56940</t>
+          <t>55160</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68303</t>
+          <t>66773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>118079</t>
+          <t>115758</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109417</t>
+          <t>107460</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126008</t>
+          <t>122985</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>85436</t>
+          <t>84066</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>85436</t>
+          <t>84066</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85436</t>
+          <t>84066</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>158926</t>
+          <t>156351</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>158926</t>
+          <t>156351</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>158926</t>
+          <t>156351</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>11756</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20887</t>
+          <t>21869</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26980</t>
+          <t>27726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>27879</t>
+          <t>29010</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22258</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>36126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>67676</t>
+          <t>76015</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62973</t>
+          <t>71400</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71131</t>
+          <t>79695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>82749</t>
+          <t>88635</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76656</t>
+          <t>82778</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87362</t>
+          <t>93596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>150424</t>
+          <t>164650</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143592</t>
+          <t>157534</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>156045</t>
+          <t>171003</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9404</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>10489</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17367</t>
+          <t>19046</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15217</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25048</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28294</t>
+          <t>29842</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24889</t>
+          <t>26391</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31052</t>
+          <t>32566</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45083</t>
+          <t>46722</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41181</t>
+          <t>41773</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48694</t>
+          <t>50330</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>73377</t>
+          <t>76564</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67793</t>
+          <t>70934</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78000</t>
+          <t>81603</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,28%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34293</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34293</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34293</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>58548</t>
+          <t>60819</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58548</t>
+          <t>60819</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58548</t>
+          <t>60819</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>92841</t>
+          <t>96820</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>92841</t>
+          <t>96820</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92841</t>
+          <t>96820</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>13643</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>22158</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16750</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>27139</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>34983</t>
+          <t>35801</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29479</t>
+          <t>29841</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41669</t>
+          <t>42598</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>46651</t>
+          <t>46581</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42429</t>
+          <t>42201</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50495</t>
+          <t>50517</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43885</t>
+          <t>45151</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39591</t>
+          <t>40170</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>49747</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>90536</t>
+          <t>91731</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83850</t>
+          <t>84934</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96040</t>
+          <t>97691</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,6%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>14496</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21518</t>
+          <t>26320</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>32259</t>
+          <t>39505</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7358</t>
+          <t>30945</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89449</t>
+          <t>48904</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>46755</t>
+          <t>56700</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>45182</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89445</t>
+          <t>68279</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>108027</t>
+          <t>133143</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>101005</t>
+          <t>124017</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>113957</t>
+          <t>139626</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>305247</t>
+          <t>123325</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>248057</t>
+          <t>113926</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330148</t>
+          <t>131885</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>413274</t>
+          <t>256468</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>370584</t>
+          <t>244889</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>444901</t>
+          <t>267986</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>122523</t>
+          <t>150337</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>122523</t>
+          <t>150337</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>122523</t>
+          <t>150337</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>337506</t>
+          <t>162830</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>337506</t>
+          <t>162830</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>337506</t>
+          <t>162830</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>460029</t>
+          <t>313168</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>460029</t>
+          <t>313168</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>460029</t>
+          <t>313168</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>12771</t>
+          <t>14869</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19008</t>
+          <t>21651</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>33936</t>
+          <t>39877</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27255</t>
+          <t>31209</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43754</t>
+          <t>48810</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>46707</t>
+          <t>54746</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36629</t>
+          <t>44284</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55616</t>
+          <t>66715</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>133704</t>
+          <t>148033</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>127467</t>
+          <t>141251</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>138145</t>
+          <t>153397</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>151683</t>
+          <t>171735</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>141865</t>
+          <t>162802</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>158364</t>
+          <t>180403</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>285387</t>
+          <t>319767</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>276478</t>
+          <t>307798</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>295465</t>
+          <t>330229</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,18%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>146475</t>
+          <t>162902</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>146475</t>
+          <t>162902</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>146475</t>
+          <t>162902</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>185619</t>
+          <t>211612</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>185619</t>
+          <t>211612</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>185619</t>
+          <t>211612</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>332094</t>
+          <t>374513</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>332094</t>
+          <t>374513</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>332094</t>
+          <t>374513</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>85110</t>
+          <t>90364</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>71839</t>
+          <t>75881</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>99136</t>
+          <t>105557</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>188049</t>
+          <t>206583</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>100373</t>
+          <t>187084</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>241687</t>
+          <t>226763</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>273160</t>
+          <t>296947</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>172260</t>
+          <t>272374</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>320343</t>
+          <t>322447</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>563210</t>
+          <t>623868</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>549184</t>
+          <t>608675</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>576481</t>
+          <t>638351</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>839761</t>
+          <t>690552</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>786123</t>
+          <t>670372</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>927437</t>
+          <t>710051</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1402970</t>
+          <t>1314421</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1355787</t>
+          <t>1288921</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1503870</t>
+          <t>1338994</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>648320</t>
+          <t>714232</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>648320</t>
+          <t>714232</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>648320</t>
+          <t>714232</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1027810</t>
+          <t>897135</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1027810</t>
+          <t>897135</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1027810</t>
+          <t>897135</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1676130</t>
+          <t>1611368</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1676130</t>
+          <t>1611368</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1676130</t>
+          <t>1611368</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
